--- a/backend/data/financials_by_company/06N.WA.xlsx
+++ b/backend/data/financials_by_company/06N.WA.xlsx
@@ -677,58 +677,58 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>838850</v>
+        <v>-176667.255855</v>
       </c>
       <c r="C2" t="n">
-        <v>0.19</v>
+        <v>0.147592</v>
       </c>
       <c r="D2" t="n">
-        <v>4577000</v>
+        <v>4523000</v>
       </c>
       <c r="E2" t="n">
-        <v>4415000</v>
+        <v>-1197000</v>
       </c>
       <c r="F2" t="n">
-        <v>4415000</v>
+        <v>-1197000</v>
       </c>
       <c r="G2" t="n">
-        <v>3784000</v>
+        <v>1192000</v>
       </c>
       <c r="H2" t="n">
-        <v>3872000</v>
+        <v>864000</v>
       </c>
       <c r="I2" t="n">
-        <v>12619000</v>
+        <v>2978000</v>
       </c>
       <c r="J2" t="n">
-        <v>8992000</v>
+        <v>3326000</v>
       </c>
       <c r="K2" t="n">
-        <v>5120000</v>
+        <v>2462000</v>
       </c>
       <c r="L2" t="n">
-        <v>4969000</v>
+        <v>2098000</v>
       </c>
       <c r="M2" t="n">
-        <v>273000</v>
+        <v>199000</v>
       </c>
       <c r="N2" t="n">
-        <v>5068000</v>
+        <v>2297000</v>
       </c>
       <c r="O2" t="n">
-        <v>207850</v>
+        <v>2212332.744145</v>
       </c>
       <c r="P2" t="n">
-        <v>3784000</v>
+        <v>1192000</v>
       </c>
       <c r="Q2" t="n">
-        <v>23564000</v>
+        <v>6466000</v>
       </c>
       <c r="R2" t="n">
-        <v>715000</v>
+        <v>1348000</v>
       </c>
       <c r="S2" t="n">
         <v>13921975</v>
@@ -737,151 +737,149 @@
         <v>13921975</v>
       </c>
       <c r="U2" t="n">
-        <v>0.36</v>
+        <v>0.14</v>
       </c>
       <c r="V2" t="n">
-        <v>0.36</v>
+        <v>0.14</v>
       </c>
       <c r="W2" t="n">
-        <v>3784000</v>
+        <v>1192000</v>
       </c>
       <c r="X2" t="n">
-        <v>3784000</v>
+        <v>1192000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>3784000</v>
+        <v>1192000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-1294000</v>
+        <v>-737000</v>
       </c>
       <c r="AB2" t="n">
-        <v>5078000</v>
+        <v>1929000</v>
       </c>
       <c r="AC2" t="n">
-        <v>5078000</v>
+        <v>1929000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-231000</v>
+        <v>334000</v>
       </c>
       <c r="AE2" t="n">
-        <v>4847000</v>
+        <v>2263000</v>
       </c>
       <c r="AF2" t="n">
-        <v>155000</v>
+        <v>119000</v>
       </c>
       <c r="AG2" t="n">
-        <v>2780000</v>
+        <v>-1197000</v>
       </c>
       <c r="AH2" t="n">
-        <v>31000</v>
+        <v>135000</v>
       </c>
       <c r="AI2" t="n">
-        <v>2399000</v>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="n">
-        <v>-5210000</v>
-      </c>
+        <v>1062000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>4969000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-174000</v>
-      </c>
+        <v>2098000</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="n">
-        <v>273000</v>
+        <v>199000</v>
       </c>
       <c r="AO2" t="n">
-        <v>5068000</v>
+        <v>2297000</v>
       </c>
       <c r="AP2" t="n">
-        <v>-4412000</v>
+        <v>-523000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10945000</v>
+        <v>3488000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-161000</v>
+        <v>49000</v>
       </c>
       <c r="AS2" t="n">
-        <v>11180000</v>
+        <v>6726000</v>
       </c>
       <c r="AT2" t="n">
-        <v>4221000</v>
+        <v>1815000</v>
       </c>
       <c r="AU2" t="n">
-        <v>6959000</v>
+        <v>4911000</v>
       </c>
       <c r="AV2" t="n">
-        <v>6533000</v>
+        <v>2965000</v>
       </c>
       <c r="AW2" t="n">
-        <v>12619000</v>
+        <v>2978000</v>
       </c>
       <c r="AX2" t="n">
-        <v>19152000</v>
+        <v>5943000</v>
       </c>
       <c r="AY2" t="n">
-        <v>19152000</v>
+        <v>5943000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-710270.301006</v>
+        <v>-762850</v>
       </c>
       <c r="C3" t="n">
-        <v>0.189204</v>
+        <v>0.19</v>
       </c>
       <c r="D3" t="n">
-        <v>89205000</v>
+        <v>3472000</v>
       </c>
       <c r="E3" t="n">
-        <v>-3754000</v>
+        <v>-4015000</v>
       </c>
       <c r="F3" t="n">
-        <v>-3754000</v>
+        <v>-4015000</v>
       </c>
       <c r="G3" t="n">
-        <v>68526000</v>
+        <v>-585000</v>
       </c>
       <c r="H3" t="n">
-        <v>918000</v>
+        <v>824000</v>
       </c>
       <c r="I3" t="n">
-        <v>3254000</v>
+        <v>1296000</v>
       </c>
       <c r="J3" t="n">
-        <v>85451000</v>
+        <v>-543000</v>
       </c>
       <c r="K3" t="n">
-        <v>84533000</v>
+        <v>-1367000</v>
       </c>
       <c r="L3" t="n">
-        <v>3364000</v>
+        <v>3124000</v>
       </c>
       <c r="M3" t="n">
-        <v>116000</v>
+        <v>228000</v>
       </c>
       <c r="N3" t="n">
-        <v>3480000</v>
+        <v>3352000</v>
       </c>
       <c r="O3" t="n">
-        <v>71569729.698994</v>
+        <v>2667150</v>
       </c>
       <c r="P3" t="n">
-        <v>68526000</v>
+        <v>-585000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-77723000</v>
+        <v>8974000</v>
       </c>
       <c r="R3" t="n">
-        <v>81322000</v>
+        <v>-2435000</v>
       </c>
       <c r="S3" t="n">
         <v>13921975</v>
@@ -890,151 +888,149 @@
         <v>13921975</v>
       </c>
       <c r="U3" t="n">
-        <v>4.92</v>
+        <v>-0.05</v>
       </c>
       <c r="V3" t="n">
-        <v>4.92</v>
+        <v>-0.05</v>
       </c>
       <c r="W3" t="n">
-        <v>68526000</v>
+        <v>-585000</v>
       </c>
       <c r="X3" t="n">
-        <v>68526000</v>
+        <v>-585000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>68526000</v>
+        <v>-585000</v>
       </c>
       <c r="AA3" t="n">
-        <v>81000</v>
+        <v>49000</v>
       </c>
       <c r="AB3" t="n">
-        <v>68445000</v>
+        <v>-634000</v>
       </c>
       <c r="AC3" t="n">
-        <v>68445000</v>
+        <v>-634000</v>
       </c>
       <c r="AD3" t="n">
-        <v>15972000</v>
+        <v>-961000</v>
       </c>
       <c r="AE3" t="n">
-        <v>84417000</v>
+        <v>-1595000</v>
       </c>
       <c r="AF3" t="n">
-        <v>139000</v>
+        <v>123000</v>
       </c>
       <c r="AG3" t="n">
-        <v>1482000</v>
+        <v>-4227000</v>
       </c>
       <c r="AH3" t="n">
-        <v>168000</v>
+        <v>-97000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-1650000</v>
+        <v>2548000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
+        <v>1776000</v>
+      </c>
+      <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>3364000</v>
+        <v>3124000</v>
       </c>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="n">
-        <v>116000</v>
+        <v>228000</v>
       </c>
       <c r="AO3" t="n">
-        <v>3480000</v>
+        <v>3352000</v>
       </c>
       <c r="AP3" t="n">
-        <v>84826000</v>
+        <v>-2690000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-80977000</v>
+        <v>7678000</v>
       </c>
       <c r="AR3" t="n">
-        <v>104733000</v>
+        <v>531000</v>
       </c>
       <c r="AS3" t="n">
-        <v>6840000</v>
+        <v>8131000</v>
       </c>
       <c r="AT3" t="n">
-        <v>1987000</v>
+        <v>1968000</v>
       </c>
       <c r="AU3" t="n">
-        <v>4853000</v>
+        <v>6163000</v>
       </c>
       <c r="AV3" t="n">
-        <v>3849000</v>
+        <v>4988000</v>
       </c>
       <c r="AW3" t="n">
-        <v>3254000</v>
+        <v>1296000</v>
       </c>
       <c r="AX3" t="n">
-        <v>7103000</v>
+        <v>6284000</v>
       </c>
       <c r="AY3" t="n">
-        <v>7103000</v>
+        <v>6284000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-762850</v>
+        <v>-710270.301006</v>
       </c>
       <c r="C4" t="n">
-        <v>0.19</v>
+        <v>0.189204</v>
       </c>
       <c r="D4" t="n">
-        <v>3472000</v>
+        <v>89205000</v>
       </c>
       <c r="E4" t="n">
-        <v>-4015000</v>
+        <v>-3754000</v>
       </c>
       <c r="F4" t="n">
-        <v>-4015000</v>
+        <v>-3754000</v>
       </c>
       <c r="G4" t="n">
-        <v>-585000</v>
+        <v>68526000</v>
       </c>
       <c r="H4" t="n">
-        <v>824000</v>
+        <v>918000</v>
       </c>
       <c r="I4" t="n">
-        <v>1296000</v>
+        <v>3254000</v>
       </c>
       <c r="J4" t="n">
-        <v>-543000</v>
+        <v>85451000</v>
       </c>
       <c r="K4" t="n">
-        <v>-1367000</v>
+        <v>84533000</v>
       </c>
       <c r="L4" t="n">
-        <v>3124000</v>
+        <v>3364000</v>
       </c>
       <c r="M4" t="n">
-        <v>228000</v>
+        <v>116000</v>
       </c>
       <c r="N4" t="n">
-        <v>3352000</v>
+        <v>3480000</v>
       </c>
       <c r="O4" t="n">
-        <v>2667150</v>
+        <v>71569729.698994</v>
       </c>
       <c r="P4" t="n">
-        <v>-585000</v>
+        <v>68526000</v>
       </c>
       <c r="Q4" t="n">
-        <v>8974000</v>
+        <v>-77723000</v>
       </c>
       <c r="R4" t="n">
-        <v>-2435000</v>
+        <v>81322000</v>
       </c>
       <c r="S4" t="n">
         <v>13921975</v>
@@ -1043,149 +1039,151 @@
         <v>13921975</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.05</v>
+        <v>4.92</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.05</v>
+        <v>4.92</v>
       </c>
       <c r="W4" t="n">
-        <v>-585000</v>
+        <v>68526000</v>
       </c>
       <c r="X4" t="n">
-        <v>-585000</v>
+        <v>68526000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-585000</v>
+        <v>68526000</v>
       </c>
       <c r="AA4" t="n">
-        <v>49000</v>
+        <v>81000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-634000</v>
+        <v>68445000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-634000</v>
+        <v>68445000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-961000</v>
+        <v>15972000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-1595000</v>
+        <v>84417000</v>
       </c>
       <c r="AF4" t="n">
-        <v>123000</v>
+        <v>139000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-4227000</v>
+        <v>1482000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-97000</v>
+        <v>168000</v>
       </c>
       <c r="AI4" t="n">
-        <v>2548000</v>
+        <v>-1650000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1776000</v>
-      </c>
-      <c r="AK4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
       <c r="AL4" t="n">
-        <v>3124000</v>
+        <v>3364000</v>
       </c>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>228000</v>
+        <v>116000</v>
       </c>
       <c r="AO4" t="n">
-        <v>3352000</v>
+        <v>3480000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-2690000</v>
+        <v>84826000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7678000</v>
+        <v>-80977000</v>
       </c>
       <c r="AR4" t="n">
-        <v>531000</v>
+        <v>104733000</v>
       </c>
       <c r="AS4" t="n">
-        <v>8131000</v>
+        <v>6840000</v>
       </c>
       <c r="AT4" t="n">
-        <v>1968000</v>
+        <v>1987000</v>
       </c>
       <c r="AU4" t="n">
-        <v>6163000</v>
+        <v>4853000</v>
       </c>
       <c r="AV4" t="n">
-        <v>4988000</v>
+        <v>3849000</v>
       </c>
       <c r="AW4" t="n">
-        <v>1296000</v>
+        <v>3254000</v>
       </c>
       <c r="AX4" t="n">
-        <v>6284000</v>
+        <v>7103000</v>
       </c>
       <c r="AY4" t="n">
-        <v>6284000</v>
+        <v>7103000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-176667.255855</v>
+        <v>838850</v>
       </c>
       <c r="C5" t="n">
-        <v>0.147592</v>
+        <v>0.19</v>
       </c>
       <c r="D5" t="n">
-        <v>4523000</v>
+        <v>4577000</v>
       </c>
       <c r="E5" t="n">
-        <v>-1197000</v>
+        <v>4415000</v>
       </c>
       <c r="F5" t="n">
-        <v>-1197000</v>
+        <v>4415000</v>
       </c>
       <c r="G5" t="n">
-        <v>1192000</v>
+        <v>3784000</v>
       </c>
       <c r="H5" t="n">
-        <v>864000</v>
+        <v>3872000</v>
       </c>
       <c r="I5" t="n">
-        <v>2978000</v>
+        <v>12619000</v>
       </c>
       <c r="J5" t="n">
-        <v>3326000</v>
+        <v>8992000</v>
       </c>
       <c r="K5" t="n">
-        <v>2462000</v>
+        <v>5120000</v>
       </c>
       <c r="L5" t="n">
-        <v>2098000</v>
+        <v>4969000</v>
       </c>
       <c r="M5" t="n">
-        <v>199000</v>
+        <v>273000</v>
       </c>
       <c r="N5" t="n">
-        <v>2297000</v>
+        <v>5068000</v>
       </c>
       <c r="O5" t="n">
-        <v>2212332.744145</v>
+        <v>207850</v>
       </c>
       <c r="P5" t="n">
-        <v>1192000</v>
+        <v>3784000</v>
       </c>
       <c r="Q5" t="n">
-        <v>6466000</v>
+        <v>23564000</v>
       </c>
       <c r="R5" t="n">
-        <v>1348000</v>
+        <v>715000</v>
       </c>
       <c r="S5" t="n">
         <v>13921975</v>
@@ -1194,93 +1192,95 @@
         <v>13921975</v>
       </c>
       <c r="U5" t="n">
-        <v>0.14</v>
+        <v>0.36</v>
       </c>
       <c r="V5" t="n">
-        <v>0.14</v>
+        <v>0.36</v>
       </c>
       <c r="W5" t="n">
-        <v>1192000</v>
+        <v>3784000</v>
       </c>
       <c r="X5" t="n">
-        <v>1192000</v>
+        <v>3784000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1192000</v>
+        <v>3784000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-737000</v>
+        <v>-1294000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1929000</v>
+        <v>5078000</v>
       </c>
       <c r="AC5" t="n">
-        <v>1929000</v>
+        <v>5078000</v>
       </c>
       <c r="AD5" t="n">
-        <v>334000</v>
+        <v>-231000</v>
       </c>
       <c r="AE5" t="n">
-        <v>2263000</v>
+        <v>4847000</v>
       </c>
       <c r="AF5" t="n">
-        <v>119000</v>
+        <v>155000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-1197000</v>
+        <v>2780000</v>
       </c>
       <c r="AH5" t="n">
-        <v>135000</v>
+        <v>31000</v>
       </c>
       <c r="AI5" t="n">
-        <v>1062000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="inlineStr"/>
+        <v>2399000</v>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="n">
+        <v>-5210000</v>
+      </c>
       <c r="AL5" t="n">
-        <v>2098000</v>
-      </c>
-      <c r="AM5" t="inlineStr"/>
+        <v>4969000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-174000</v>
+      </c>
       <c r="AN5" t="n">
-        <v>199000</v>
+        <v>273000</v>
       </c>
       <c r="AO5" t="n">
-        <v>2297000</v>
+        <v>5068000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-523000</v>
+        <v>-4412000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3488000</v>
+        <v>10945000</v>
       </c>
       <c r="AR5" t="n">
-        <v>49000</v>
+        <v>-161000</v>
       </c>
       <c r="AS5" t="n">
-        <v>6726000</v>
+        <v>11180000</v>
       </c>
       <c r="AT5" t="n">
-        <v>1815000</v>
+        <v>4221000</v>
       </c>
       <c r="AU5" t="n">
-        <v>4911000</v>
+        <v>6959000</v>
       </c>
       <c r="AV5" t="n">
-        <v>2965000</v>
+        <v>6533000</v>
       </c>
       <c r="AW5" t="n">
-        <v>2978000</v>
+        <v>12619000</v>
       </c>
       <c r="AX5" t="n">
-        <v>5943000</v>
+        <v>19152000</v>
       </c>
       <c r="AY5" t="n">
-        <v>5943000</v>
+        <v>19152000</v>
       </c>
     </row>
   </sheetData>
@@ -1611,7 +1611,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>180000</v>
@@ -1622,42 +1622,44 @@
       <c r="D2" t="n">
         <v>13921975</v>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>1297000</v>
+      </c>
       <c r="F2" t="n">
-        <v>1510000</v>
+        <v>2943000</v>
       </c>
       <c r="G2" t="n">
-        <v>81563000</v>
+        <v>26546000</v>
       </c>
       <c r="H2" t="n">
-        <v>97409000</v>
+        <v>28364000</v>
       </c>
       <c r="I2" t="n">
-        <v>58041000</v>
+        <v>9974000</v>
       </c>
       <c r="J2" t="n">
-        <v>81563000</v>
+        <v>26546000</v>
       </c>
       <c r="K2" t="n">
-        <v>97409000</v>
+        <v>28364000</v>
       </c>
       <c r="L2" t="n">
-        <v>97409000</v>
+        <v>28364000</v>
       </c>
       <c r="M2" t="n">
-        <v>101764000</v>
+        <v>31508000</v>
       </c>
       <c r="N2" t="n">
-        <v>4355000</v>
+        <v>3144000</v>
       </c>
       <c r="O2" t="n">
-        <v>97409000</v>
+        <v>28364000</v>
       </c>
       <c r="P2" t="n">
         <v>468000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-17127000</v>
+        <v>-36888000</v>
       </c>
       <c r="R2" t="n">
         <v>20056000</v>
@@ -1669,128 +1671,128 @@
         <v>13922000</v>
       </c>
       <c r="U2" t="n">
-        <v>7484000</v>
+        <v>6157000</v>
       </c>
       <c r="V2" t="n">
-        <v>701000</v>
+        <v>227000</v>
       </c>
       <c r="W2" t="n">
-        <v>36000</v>
+        <v>22000</v>
       </c>
       <c r="X2" t="n">
-        <v>665000</v>
+        <v>205000</v>
       </c>
       <c r="Y2" t="n">
-        <v>6783000</v>
+        <v>5930000</v>
       </c>
       <c r="Z2" t="n">
-        <v>840000</v>
+        <v>448000</v>
       </c>
       <c r="AA2" t="n">
-        <v>845000</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
+        <v>2738000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2738000</v>
+      </c>
       <c r="AC2" t="n">
-        <v>1538000</v>
+        <v>1327000</v>
       </c>
       <c r="AD2" t="n">
-        <v>1467000</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
+        <v>905000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>19000</v>
+      </c>
       <c r="AF2" t="n">
-        <v>1467000</v>
+        <v>886000</v>
       </c>
       <c r="AG2" t="n">
-        <v>109248000</v>
+        <v>37665000</v>
       </c>
       <c r="AH2" t="n">
-        <v>44424000</v>
+        <v>21761000</v>
       </c>
       <c r="AI2" t="n">
-        <v>1822000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>25230000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>25230000</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
+        <v>1473000</v>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="n">
+        <v>12248000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>12248000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>5230000</v>
+      </c>
       <c r="AO2" t="n">
-        <v>15846000</v>
+        <v>1818000</v>
       </c>
       <c r="AP2" t="n">
-        <v>15459000</v>
+        <v>1431000</v>
       </c>
       <c r="AQ2" t="n">
         <v>387000</v>
       </c>
       <c r="AR2" t="n">
-        <v>1526000</v>
+        <v>751000</v>
       </c>
       <c r="AS2" t="n">
-        <v>-5865000</v>
+        <v>-1390000</v>
       </c>
       <c r="AT2" t="n">
-        <v>7391000</v>
+        <v>2141000</v>
       </c>
       <c r="AU2" t="n">
         <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>365000</v>
+        <v>734000</v>
       </c>
       <c r="AW2" t="n">
-        <v>5220000</v>
+        <v>894000</v>
       </c>
       <c r="AX2" t="n">
-        <v>1227000</v>
+        <v>862000</v>
       </c>
       <c r="AY2" t="n">
-        <v>579000</v>
+        <v>513000</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>64824000</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>128000</v>
-      </c>
+        <v>15904000</v>
+      </c>
+      <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="n">
-        <v>107000</v>
+        <v>20000</v>
       </c>
       <c r="BD2" t="n">
-        <v>42848000</v>
+        <v>12592000</v>
       </c>
       <c r="BE2" t="n">
-        <v>299000</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>3153000</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>-115000</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>3268000</v>
-      </c>
+        <v>1067000</v>
+      </c>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="n">
-        <v>18289000</v>
+        <v>2225000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>11981000</v>
+        <v>784000</v>
       </c>
       <c r="BK2" t="n">
-        <v>6308000</v>
+        <v>1441000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>180000</v>
@@ -1803,40 +1805,40 @@
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>1247000</v>
+        <v>1367000</v>
       </c>
       <c r="G3" t="n">
-        <v>91745000</v>
+        <v>23345000</v>
       </c>
       <c r="H3" t="n">
-        <v>93625000</v>
+        <v>25099000</v>
       </c>
       <c r="I3" t="n">
-        <v>75168000</v>
+        <v>11032000</v>
       </c>
       <c r="J3" t="n">
-        <v>91745000</v>
+        <v>23345000</v>
       </c>
       <c r="K3" t="n">
-        <v>93625000</v>
+        <v>25099000</v>
       </c>
       <c r="L3" t="n">
-        <v>93625000</v>
+        <v>25099000</v>
       </c>
       <c r="M3" t="n">
-        <v>96639000</v>
+        <v>28194000</v>
       </c>
       <c r="N3" t="n">
-        <v>3014000</v>
+        <v>3095000</v>
       </c>
       <c r="O3" t="n">
-        <v>93625000</v>
+        <v>25099000</v>
       </c>
       <c r="P3" t="n">
         <v>468000</v>
       </c>
       <c r="Q3" t="n">
-        <v>32746000</v>
+        <v>-40282000</v>
       </c>
       <c r="R3" t="n">
         <v>20056000</v>
@@ -1848,87 +1850,89 @@
         <v>13922000</v>
       </c>
       <c r="U3" t="n">
-        <v>3628000</v>
+        <v>5238000</v>
       </c>
       <c r="V3" t="n">
-        <v>760000</v>
+        <v>197000</v>
       </c>
       <c r="W3" t="n">
-        <v>30000</v>
+        <v>26000</v>
       </c>
       <c r="X3" t="n">
-        <v>730000</v>
+        <v>171000</v>
       </c>
       <c r="Y3" t="n">
-        <v>2868000</v>
+        <v>5041000</v>
       </c>
       <c r="Z3" t="n">
-        <v>142000</v>
+        <v>881000</v>
       </c>
       <c r="AA3" t="n">
-        <v>517000</v>
+        <v>1196000</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>1023000</v>
+        <v>1630000</v>
       </c>
       <c r="AD3" t="n">
-        <v>412000</v>
+        <v>1132000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="AF3" t="n">
-        <v>412000</v>
+        <v>1126000</v>
       </c>
       <c r="AG3" t="n">
-        <v>100267000</v>
+        <v>33432000</v>
       </c>
       <c r="AH3" t="n">
-        <v>22231000</v>
+        <v>17359000</v>
       </c>
       <c r="AI3" t="n">
-        <v>2613000</v>
+        <v>2442000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>16376000</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>16376000</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>12420000</v>
+        <v>12522000</v>
       </c>
       <c r="AM3" t="n">
-        <v>12420000</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>12522000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
       <c r="AO3" t="n">
-        <v>1880000</v>
+        <v>1754000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1493000</v>
+        <v>1367000</v>
       </c>
       <c r="AQ3" t="n">
         <v>387000</v>
       </c>
       <c r="AR3" t="n">
-        <v>1362000</v>
+        <v>593000</v>
       </c>
       <c r="AS3" t="n">
-        <v>-2713000</v>
+        <v>-2298000</v>
       </c>
       <c r="AT3" t="n">
-        <v>4075000</v>
+        <v>2891000</v>
       </c>
       <c r="AU3" t="n">
         <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>147000</v>
+        <v>166000</v>
       </c>
       <c r="AW3" t="n">
-        <v>2553000</v>
+        <v>1350000</v>
       </c>
       <c r="AX3" t="n">
         <v>862000</v>
@@ -1940,42 +1944,38 @@
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>78036000</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>86000</v>
-      </c>
+        <v>16073000</v>
+      </c>
+      <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="n">
         <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>30326000</v>
+        <v>13102000</v>
       </c>
       <c r="BE3" t="n">
-        <v>482000</v>
+        <v>2000</v>
       </c>
       <c r="BF3" t="n">
-        <v>661000</v>
+        <v>804000</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
       </c>
       <c r="BH3" t="n">
-        <v>661000</v>
+        <v>804000</v>
       </c>
       <c r="BI3" t="n">
-        <v>46475000</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>21383000</v>
-      </c>
+        <v>2165000</v>
+      </c>
+      <c r="BJ3" t="inlineStr"/>
       <c r="BK3" t="n">
-        <v>25092000</v>
+        <v>2165000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>180000</v>
@@ -1988,40 +1988,40 @@
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>1367000</v>
+        <v>1247000</v>
       </c>
       <c r="G4" t="n">
-        <v>23345000</v>
+        <v>91745000</v>
       </c>
       <c r="H4" t="n">
-        <v>25099000</v>
+        <v>93625000</v>
       </c>
       <c r="I4" t="n">
-        <v>11032000</v>
+        <v>75168000</v>
       </c>
       <c r="J4" t="n">
-        <v>23345000</v>
+        <v>91745000</v>
       </c>
       <c r="K4" t="n">
-        <v>25099000</v>
+        <v>93625000</v>
       </c>
       <c r="L4" t="n">
-        <v>25099000</v>
+        <v>93625000</v>
       </c>
       <c r="M4" t="n">
-        <v>28194000</v>
+        <v>96639000</v>
       </c>
       <c r="N4" t="n">
-        <v>3095000</v>
+        <v>3014000</v>
       </c>
       <c r="O4" t="n">
-        <v>25099000</v>
+        <v>93625000</v>
       </c>
       <c r="P4" t="n">
         <v>468000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-40282000</v>
+        <v>32746000</v>
       </c>
       <c r="R4" t="n">
         <v>20056000</v>
@@ -2033,89 +2033,87 @@
         <v>13922000</v>
       </c>
       <c r="U4" t="n">
-        <v>5238000</v>
+        <v>3628000</v>
       </c>
       <c r="V4" t="n">
-        <v>197000</v>
+        <v>760000</v>
       </c>
       <c r="W4" t="n">
-        <v>26000</v>
+        <v>30000</v>
       </c>
       <c r="X4" t="n">
-        <v>171000</v>
+        <v>730000</v>
       </c>
       <c r="Y4" t="n">
-        <v>5041000</v>
+        <v>2868000</v>
       </c>
       <c r="Z4" t="n">
-        <v>881000</v>
+        <v>142000</v>
       </c>
       <c r="AA4" t="n">
-        <v>1196000</v>
+        <v>517000</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>1630000</v>
+        <v>1023000</v>
       </c>
       <c r="AD4" t="n">
-        <v>1132000</v>
+        <v>412000</v>
       </c>
       <c r="AE4" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1126000</v>
+        <v>412000</v>
       </c>
       <c r="AG4" t="n">
-        <v>33432000</v>
+        <v>100267000</v>
       </c>
       <c r="AH4" t="n">
-        <v>17359000</v>
+        <v>22231000</v>
       </c>
       <c r="AI4" t="n">
-        <v>2442000</v>
+        <v>2613000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>16376000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>16376000</v>
       </c>
       <c r="AL4" t="n">
-        <v>12522000</v>
+        <v>12420000</v>
       </c>
       <c r="AM4" t="n">
-        <v>12522000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
+        <v>12420000</v>
+      </c>
+      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>1754000</v>
+        <v>1880000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1367000</v>
+        <v>1493000</v>
       </c>
       <c r="AQ4" t="n">
         <v>387000</v>
       </c>
       <c r="AR4" t="n">
-        <v>593000</v>
+        <v>1362000</v>
       </c>
       <c r="AS4" t="n">
-        <v>-2298000</v>
+        <v>-2713000</v>
       </c>
       <c r="AT4" t="n">
-        <v>2891000</v>
+        <v>4075000</v>
       </c>
       <c r="AU4" t="n">
         <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>166000</v>
+        <v>147000</v>
       </c>
       <c r="AW4" t="n">
-        <v>1350000</v>
+        <v>2553000</v>
       </c>
       <c r="AX4" t="n">
         <v>862000</v>
@@ -2127,38 +2125,42 @@
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>16073000</v>
-      </c>
-      <c r="BB4" t="inlineStr"/>
+        <v>78036000</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>86000</v>
+      </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>13102000</v>
+        <v>30326000</v>
       </c>
       <c r="BE4" t="n">
-        <v>2000</v>
+        <v>482000</v>
       </c>
       <c r="BF4" t="n">
-        <v>804000</v>
+        <v>661000</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
       </c>
       <c r="BH4" t="n">
-        <v>804000</v>
+        <v>661000</v>
       </c>
       <c r="BI4" t="n">
-        <v>2165000</v>
-      </c>
-      <c r="BJ4" t="inlineStr"/>
+        <v>46475000</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>21383000</v>
+      </c>
       <c r="BK4" t="n">
-        <v>2165000</v>
+        <v>25092000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>180000</v>
@@ -2169,44 +2171,42 @@
       <c r="D5" t="n">
         <v>13921975</v>
       </c>
-      <c r="E5" t="n">
-        <v>1297000</v>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>2943000</v>
+        <v>1510000</v>
       </c>
       <c r="G5" t="n">
-        <v>26546000</v>
+        <v>81563000</v>
       </c>
       <c r="H5" t="n">
-        <v>28364000</v>
+        <v>97409000</v>
       </c>
       <c r="I5" t="n">
-        <v>9974000</v>
+        <v>58041000</v>
       </c>
       <c r="J5" t="n">
-        <v>26546000</v>
+        <v>81563000</v>
       </c>
       <c r="K5" t="n">
-        <v>28364000</v>
+        <v>97409000</v>
       </c>
       <c r="L5" t="n">
-        <v>28364000</v>
+        <v>97409000</v>
       </c>
       <c r="M5" t="n">
-        <v>31508000</v>
+        <v>101764000</v>
       </c>
       <c r="N5" t="n">
-        <v>3144000</v>
+        <v>4355000</v>
       </c>
       <c r="O5" t="n">
-        <v>28364000</v>
+        <v>97409000</v>
       </c>
       <c r="P5" t="n">
         <v>468000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-36888000</v>
+        <v>-17127000</v>
       </c>
       <c r="R5" t="n">
         <v>20056000</v>
@@ -2218,123 +2218,123 @@
         <v>13922000</v>
       </c>
       <c r="U5" t="n">
-        <v>6157000</v>
+        <v>7484000</v>
       </c>
       <c r="V5" t="n">
-        <v>227000</v>
+        <v>701000</v>
       </c>
       <c r="W5" t="n">
-        <v>22000</v>
+        <v>36000</v>
       </c>
       <c r="X5" t="n">
-        <v>205000</v>
+        <v>665000</v>
       </c>
       <c r="Y5" t="n">
-        <v>5930000</v>
+        <v>6783000</v>
       </c>
       <c r="Z5" t="n">
-        <v>448000</v>
+        <v>840000</v>
       </c>
       <c r="AA5" t="n">
-        <v>2738000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2738000</v>
-      </c>
+        <v>845000</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>1327000</v>
+        <v>1538000</v>
       </c>
       <c r="AD5" t="n">
-        <v>905000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>19000</v>
-      </c>
+        <v>1467000</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>886000</v>
+        <v>1467000</v>
       </c>
       <c r="AG5" t="n">
-        <v>37665000</v>
+        <v>109248000</v>
       </c>
       <c r="AH5" t="n">
-        <v>21761000</v>
+        <v>44424000</v>
       </c>
       <c r="AI5" t="n">
-        <v>1473000</v>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="n">
-        <v>12248000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>12248000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>5230000</v>
-      </c>
+        <v>1822000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>25230000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>25230000</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>1818000</v>
+        <v>15846000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1431000</v>
+        <v>15459000</v>
       </c>
       <c r="AQ5" t="n">
         <v>387000</v>
       </c>
       <c r="AR5" t="n">
-        <v>751000</v>
+        <v>1526000</v>
       </c>
       <c r="AS5" t="n">
-        <v>-1390000</v>
+        <v>-5865000</v>
       </c>
       <c r="AT5" t="n">
-        <v>2141000</v>
+        <v>7391000</v>
       </c>
       <c r="AU5" t="n">
         <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>734000</v>
+        <v>365000</v>
       </c>
       <c r="AW5" t="n">
-        <v>894000</v>
+        <v>5220000</v>
       </c>
       <c r="AX5" t="n">
-        <v>862000</v>
+        <v>1227000</v>
       </c>
       <c r="AY5" t="n">
-        <v>513000</v>
+        <v>579000</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>15904000</v>
-      </c>
-      <c r="BB5" t="inlineStr"/>
+        <v>64824000</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>128000</v>
+      </c>
       <c r="BC5" t="n">
-        <v>20000</v>
+        <v>107000</v>
       </c>
       <c r="BD5" t="n">
-        <v>12592000</v>
+        <v>42848000</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>299000</v>
       </c>
       <c r="BF5" t="n">
-        <v>1067000</v>
-      </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+        <v>3153000</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>-115000</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3268000</v>
+      </c>
       <c r="BI5" t="n">
-        <v>2225000</v>
+        <v>18289000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>784000</v>
+        <v>11981000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1441000</v>
+        <v>6308000</v>
       </c>
     </row>
   </sheetData>
@@ -2590,558 +2590,558 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-3126000</v>
+        <v>-1940000</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>-197000</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="E2" t="n">
-        <v>-3095000</v>
+        <v>-19000</v>
       </c>
       <c r="F2" t="n">
-        <v>6308000</v>
+        <v>1441000</v>
       </c>
       <c r="G2" t="n">
-        <v>24770000</v>
+        <v>2459000</v>
       </c>
       <c r="H2" t="n">
-        <v>1000</v>
+        <v>-4000</v>
       </c>
       <c r="I2" t="n">
-        <v>-18463000</v>
+        <v>-1014000</v>
       </c>
       <c r="J2" t="n">
-        <v>-624000</v>
+        <v>1282000</v>
       </c>
       <c r="K2" t="n">
-        <v>19000</v>
+        <v>1430000</v>
       </c>
       <c r="L2" t="n">
-        <v>-202000</v>
+        <v>-5000</v>
       </c>
       <c r="M2" t="n">
-        <v>11000</v>
+        <v>-97000</v>
       </c>
       <c r="N2" t="n">
-        <v>11000</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-97000</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-197000</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="S2" t="n">
-        <v>-17808000</v>
+        <v>-375000</v>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>1119000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>27000</v>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>-5410000</v>
+        <v>221000</v>
       </c>
       <c r="X2" t="n">
-        <v>7962000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-13372000</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
+        <v>221000</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
       <c r="AB2" t="n">
-        <v>-266000</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-800000</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-2989000</v>
+        <v>-1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>7000</v>
+        <v>18000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-2996000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-99000</v>
-      </c>
+        <v>-19000</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>-31000</v>
+        <v>-1921000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-110000</v>
+        <v>-89000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>852000</v>
+        <v>-805000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-48000</v>
+        <v>1902000</v>
       </c>
       <c r="AL2" t="n">
-        <v>375000</v>
+        <v>-212000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-67000</v>
+        <v>-1740000</v>
       </c>
       <c r="AN2" t="n">
-        <v>35000</v>
+        <v>-20000</v>
       </c>
       <c r="AO2" t="n">
-        <v>557000</v>
+        <v>-735000</v>
       </c>
       <c r="AP2" t="n">
-        <v>-8202000</v>
+        <v>-1546000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3872000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>3112000</v>
-      </c>
+        <v>864000</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
-        <v>760000</v>
+        <v>864000</v>
       </c>
       <c r="AT2" t="n">
-        <v>-1661000</v>
+        <v>-1885000</v>
       </c>
       <c r="AU2" t="n">
-        <v>-10000</v>
+        <v>-4000</v>
       </c>
       <c r="AV2" t="n">
-        <v>4847000</v>
+        <v>2263000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>65544000</v>
+        <v>-1814000</v>
       </c>
       <c r="C3" t="n">
-        <v>-1200000</v>
+        <v>-2100000</v>
       </c>
       <c r="D3" t="n">
-        <v>500000</v>
+        <v>2890000</v>
       </c>
       <c r="E3" t="n">
-        <v>-640000</v>
+        <v>-465000</v>
       </c>
       <c r="F3" t="n">
-        <v>24770000</v>
+        <v>2165000</v>
       </c>
       <c r="G3" t="n">
-        <v>2165000</v>
+        <v>1441000</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="I3" t="n">
-        <v>22605000</v>
+        <v>719000</v>
       </c>
       <c r="J3" t="n">
-        <v>-951000</v>
+        <v>739000</v>
       </c>
       <c r="K3" t="n">
-        <v>192000</v>
+        <v>288000</v>
       </c>
       <c r="L3" t="n">
-        <v>-113000</v>
+        <v>-233000</v>
       </c>
       <c r="M3" t="n">
-        <v>-685000</v>
+        <v>810000</v>
       </c>
       <c r="N3" t="n">
-        <v>15000</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
+        <v>20000</v>
+      </c>
+      <c r="O3" t="n">
+        <v>20000</v>
+      </c>
       <c r="P3" t="n">
-        <v>-700000</v>
+        <v>790000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1200000</v>
+        <v>-2100000</v>
       </c>
       <c r="R3" t="n">
-        <v>500000</v>
+        <v>2890000</v>
       </c>
       <c r="S3" t="n">
-        <v>-42628000</v>
-      </c>
-      <c r="T3" t="inlineStr"/>
+        <v>1329000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-461000</v>
+      </c>
       <c r="U3" t="n">
-        <v>972000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
+        <v>12000</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>-24417000</v>
+        <v>747000</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>784000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-24417000</v>
+        <v>-37000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1145000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
+        <v>1145000</v>
+      </c>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
-        <v>-598000</v>
+        <v>-394000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>67000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-598000</v>
+        <v>-461000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-42000</v>
+        <v>-4000</v>
       </c>
       <c r="AH3" t="n">
-        <v>66184000</v>
+        <v>-1349000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-16603000</v>
+        <v>-23000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>494000</v>
+        <v>886000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-262000</v>
+        <v>-194000</v>
       </c>
       <c r="AL3" t="n">
-        <v>29000</v>
+        <v>26000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1513000</v>
+        <v>240000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="AO3" t="n">
-        <v>2240000</v>
+        <v>794000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-2505000</v>
+        <v>-726000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>918000</v>
+        <v>824000</v>
       </c>
       <c r="AR3" t="n">
-        <v>472000</v>
+        <v>525000</v>
       </c>
       <c r="AS3" t="n">
-        <v>446000</v>
+        <v>299000</v>
       </c>
       <c r="AT3" t="n">
-        <v>-704000</v>
+        <v>-952000</v>
       </c>
       <c r="AU3" t="n">
-        <v>10000</v>
+        <v>-5000</v>
       </c>
       <c r="AV3" t="n">
-        <v>84417000</v>
+        <v>-1595000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-1814000</v>
+        <v>65544000</v>
       </c>
       <c r="C4" t="n">
-        <v>-2100000</v>
+        <v>-1200000</v>
       </c>
       <c r="D4" t="n">
-        <v>2890000</v>
+        <v>500000</v>
       </c>
       <c r="E4" t="n">
-        <v>-465000</v>
+        <v>-640000</v>
       </c>
       <c r="F4" t="n">
+        <v>24770000</v>
+      </c>
+      <c r="G4" t="n">
         <v>2165000</v>
       </c>
-      <c r="G4" t="n">
-        <v>1441000</v>
-      </c>
       <c r="H4" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>719000</v>
+        <v>22605000</v>
       </c>
       <c r="J4" t="n">
-        <v>739000</v>
+        <v>-951000</v>
       </c>
       <c r="K4" t="n">
-        <v>288000</v>
+        <v>192000</v>
       </c>
       <c r="L4" t="n">
-        <v>-233000</v>
+        <v>-113000</v>
       </c>
       <c r="M4" t="n">
-        <v>810000</v>
+        <v>-685000</v>
       </c>
       <c r="N4" t="n">
-        <v>20000</v>
-      </c>
-      <c r="O4" t="n">
-        <v>20000</v>
-      </c>
+        <v>15000</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>790000</v>
+        <v>-700000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2100000</v>
+        <v>-1200000</v>
       </c>
       <c r="R4" t="n">
-        <v>2890000</v>
+        <v>500000</v>
       </c>
       <c r="S4" t="n">
-        <v>1329000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-461000</v>
-      </c>
+        <v>-42628000</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>12000</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
+        <v>972000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
       <c r="W4" t="n">
-        <v>747000</v>
+        <v>-24417000</v>
       </c>
       <c r="X4" t="n">
-        <v>784000</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-37000</v>
+        <v>-24417000</v>
       </c>
       <c r="Z4" t="n">
-        <v>1145000</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1145000</v>
-      </c>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
       <c r="AD4" t="n">
-        <v>-394000</v>
+        <v>-598000</v>
       </c>
       <c r="AE4" t="n">
-        <v>67000</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>-461000</v>
+        <v>-598000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-4000</v>
+        <v>-42000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-1349000</v>
+        <v>66184000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-23000</v>
+        <v>-16603000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>886000</v>
+        <v>494000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-194000</v>
+        <v>-262000</v>
       </c>
       <c r="AL4" t="n">
-        <v>26000</v>
+        <v>29000</v>
       </c>
       <c r="AM4" t="n">
-        <v>240000</v>
+        <v>-1513000</v>
       </c>
       <c r="AN4" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>794000</v>
+        <v>2240000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-726000</v>
+        <v>-2505000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>824000</v>
+        <v>918000</v>
       </c>
       <c r="AR4" t="n">
-        <v>525000</v>
+        <v>472000</v>
       </c>
       <c r="AS4" t="n">
-        <v>299000</v>
+        <v>446000</v>
       </c>
       <c r="AT4" t="n">
-        <v>-952000</v>
+        <v>-704000</v>
       </c>
       <c r="AU4" t="n">
-        <v>-5000</v>
+        <v>10000</v>
       </c>
       <c r="AV4" t="n">
-        <v>-1595000</v>
+        <v>84417000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-1940000</v>
+        <v>-3126000</v>
       </c>
       <c r="C5" t="n">
-        <v>-197000</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-19000</v>
+        <v>-3095000</v>
       </c>
       <c r="F5" t="n">
-        <v>1441000</v>
+        <v>6308000</v>
       </c>
       <c r="G5" t="n">
-        <v>2459000</v>
+        <v>24770000</v>
       </c>
       <c r="H5" t="n">
-        <v>-4000</v>
+        <v>1000</v>
       </c>
       <c r="I5" t="n">
-        <v>-1014000</v>
+        <v>-18463000</v>
       </c>
       <c r="J5" t="n">
-        <v>1282000</v>
+        <v>-624000</v>
       </c>
       <c r="K5" t="n">
-        <v>1430000</v>
+        <v>19000</v>
       </c>
       <c r="L5" t="n">
-        <v>-5000</v>
+        <v>-202000</v>
       </c>
       <c r="M5" t="n">
-        <v>-97000</v>
+        <v>11000</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
+        <v>11000</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>-97000</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-197000</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-375000</v>
+        <v>-17808000</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
+        <v>1119000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>27000</v>
+      </c>
       <c r="W5" t="n">
-        <v>221000</v>
+        <v>-5410000</v>
       </c>
       <c r="X5" t="n">
-        <v>221000</v>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
+        <v>7962000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-13372000</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>-266000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>-800000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-1000</v>
+        <v>-2989000</v>
       </c>
       <c r="AE5" t="n">
-        <v>18000</v>
+        <v>7000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-19000</v>
-      </c>
-      <c r="AG5" t="inlineStr"/>
+        <v>-2996000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-99000</v>
+      </c>
       <c r="AH5" t="n">
-        <v>-1921000</v>
+        <v>-31000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-89000</v>
+        <v>-110000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-805000</v>
+        <v>852000</v>
       </c>
       <c r="AK5" t="n">
-        <v>1902000</v>
+        <v>-48000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-212000</v>
+        <v>375000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1740000</v>
+        <v>-67000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-20000</v>
+        <v>35000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-735000</v>
+        <v>557000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1546000</v>
+        <v>-8202000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>864000</v>
-      </c>
-      <c r="AR5" t="inlineStr"/>
+        <v>3872000</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>3112000</v>
+      </c>
       <c r="AS5" t="n">
-        <v>864000</v>
+        <v>760000</v>
       </c>
       <c r="AT5" t="n">
-        <v>-1885000</v>
+        <v>-1661000</v>
       </c>
       <c r="AU5" t="n">
-        <v>-4000</v>
+        <v>-10000</v>
       </c>
       <c r="AV5" t="n">
-        <v>2263000</v>
+        <v>4847000</v>
       </c>
     </row>
   </sheetData>
@@ -3155,7 +3155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EE2"/>
+  <dimension ref="A1:EG2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3476,360 +3476,370 @@
       </c>
       <c r="BL1" t="inlineStr">
         <is>
-          <t>earningsQuarterlyGrowth</t>
+          <t>netIncomeToCommon</t>
         </is>
       </c>
       <c r="BM1" t="inlineStr">
         <is>
-          <t>netIncomeToCommon</t>
+          <t>trailingEps</t>
         </is>
       </c>
       <c r="BN1" t="inlineStr">
         <is>
-          <t>trailingEps</t>
+          <t>lastSplitFactor</t>
         </is>
       </c>
       <c r="BO1" t="inlineStr">
         <is>
-          <t>lastSplitFactor</t>
+          <t>lastSplitDate</t>
         </is>
       </c>
       <c r="BP1" t="inlineStr">
         <is>
-          <t>lastSplitDate</t>
+          <t>enterpriseToRevenue</t>
         </is>
       </c>
       <c r="BQ1" t="inlineStr">
         <is>
-          <t>enterpriseToRevenue</t>
+          <t>enterpriseToEbitda</t>
         </is>
       </c>
       <c r="BR1" t="inlineStr">
         <is>
-          <t>enterpriseToEbitda</t>
+          <t>52WeekChange</t>
         </is>
       </c>
       <c r="BS1" t="inlineStr">
         <is>
-          <t>52WeekChange</t>
+          <t>SandP52WeekChange</t>
         </is>
       </c>
       <c r="BT1" t="inlineStr">
         <is>
-          <t>SandP52WeekChange</t>
+          <t>lastDividendValue</t>
         </is>
       </c>
       <c r="BU1" t="inlineStr">
         <is>
-          <t>lastDividendValue</t>
+          <t>lastDividendDate</t>
         </is>
       </c>
       <c r="BV1" t="inlineStr">
         <is>
-          <t>lastDividendDate</t>
+          <t>quoteType</t>
         </is>
       </c>
       <c r="BW1" t="inlineStr">
         <is>
-          <t>quoteType</t>
+          <t>currentPrice</t>
         </is>
       </c>
       <c r="BX1" t="inlineStr">
         <is>
-          <t>currentPrice</t>
+          <t>recommendationKey</t>
         </is>
       </c>
       <c r="BY1" t="inlineStr">
         <is>
-          <t>recommendationKey</t>
+          <t>totalCash</t>
         </is>
       </c>
       <c r="BZ1" t="inlineStr">
         <is>
-          <t>totalCash</t>
+          <t>totalCashPerShare</t>
         </is>
       </c>
       <c r="CA1" t="inlineStr">
         <is>
-          <t>totalCashPerShare</t>
+          <t>ebitda</t>
         </is>
       </c>
       <c r="CB1" t="inlineStr">
         <is>
-          <t>ebitda</t>
+          <t>totalDebt</t>
         </is>
       </c>
       <c r="CC1" t="inlineStr">
         <is>
-          <t>totalDebt</t>
+          <t>quickRatio</t>
         </is>
       </c>
       <c r="CD1" t="inlineStr">
         <is>
-          <t>quickRatio</t>
+          <t>currentRatio</t>
         </is>
       </c>
       <c r="CE1" t="inlineStr">
         <is>
-          <t>currentRatio</t>
+          <t>totalRevenue</t>
         </is>
       </c>
       <c r="CF1" t="inlineStr">
         <is>
-          <t>totalRevenue</t>
+          <t>debtToEquity</t>
         </is>
       </c>
       <c r="CG1" t="inlineStr">
         <is>
-          <t>debtToEquity</t>
+          <t>revenuePerShare</t>
         </is>
       </c>
       <c r="CH1" t="inlineStr">
         <is>
-          <t>revenuePerShare</t>
+          <t>returnOnAssets</t>
         </is>
       </c>
       <c r="CI1" t="inlineStr">
         <is>
+          <t>returnOnEquity</t>
+        </is>
+      </c>
+      <c r="CJ1" t="inlineStr">
+        <is>
           <t>grossProfits</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
+        <is>
+          <t>freeCashflow</t>
+        </is>
+      </c>
+      <c r="CL1" t="inlineStr">
         <is>
           <t>operatingCashflow</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>revenueGrowth</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>grossMargins</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>ebitdaMargins</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>operatingMargins</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>financialCurrency</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>typeDisp</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>quoteSourceName</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>triggerable</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>customPriceAlertConfidence</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -3907,7 +3917,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -3926,28 +3936,28 @@
         <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="U2" t="n">
-        <v>2.35</v>
+        <v>2.52</v>
       </c>
       <c r="V2" t="n">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="W2" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="X2" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.35</v>
+        <v>2.52</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="AB2" t="n">
         <v>1193788800</v>
@@ -3956,37 +3966,37 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.046</v>
+        <v>0.024</v>
       </c>
       <c r="AE2" t="n">
-        <v>19.833334</v>
+        <v>20.833334</v>
       </c>
       <c r="AF2" t="n">
-        <v>1907</v>
+        <v>5929</v>
       </c>
       <c r="AG2" t="n">
-        <v>1907</v>
+        <v>5929</v>
       </c>
       <c r="AH2" t="n">
-        <v>6855</v>
+        <v>6231</v>
       </c>
       <c r="AI2" t="n">
-        <v>5581</v>
+        <v>7945</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5581</v>
+        <v>7945</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AM2" t="n">
-        <v>32705902</v>
+        <v>34354936</v>
       </c>
       <c r="AN2" t="n">
-        <v>32705900</v>
+        <v>34629777</v>
       </c>
       <c r="AO2" t="n">
         <v>2.33</v>
@@ -4001,13 +4011,13 @@
         <v>0.15</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.9211407</v>
+        <v>1.6689305</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.4326</v>
+        <v>2.4286</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.5967</v>
+        <v>2.59605</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -4024,13 +4034,13 @@
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-11799581</v>
+        <v>-25978062</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0.119619995</v>
+        <v>0.15248999</v>
       </c>
       <c r="BB2" t="n">
-        <v>9988629</v>
+        <v>10168649</v>
       </c>
       <c r="BC2" t="n">
         <v>13741975</v>
@@ -4045,278 +4055,284 @@
         <v>13741975</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.203</v>
+        <v>7.36</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.3304179</v>
+        <v>0.3396739</v>
       </c>
       <c r="BI2" t="n">
-        <v>1735603200</v>
+        <v>1767139200</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1767139200</v>
+        <v>1798675200</v>
       </c>
       <c r="BK2" t="n">
-        <v>1759190400</v>
+        <v>1774915200</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.474</v>
+        <v>3139000</v>
       </c>
       <c r="BM2" t="n">
-        <v>-795000</v>
-      </c>
-      <c r="BN2" t="n">
         <v>0.12</v>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>1:10</t>
         </is>
       </c>
+      <c r="BO2" t="n">
+        <v>1397433600</v>
+      </c>
       <c r="BP2" t="n">
-        <v>1397433600</v>
+        <v>-1.262</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-1.775</v>
+        <v>-0.9360000000000001</v>
       </c>
       <c r="BR2" t="n">
-        <v>-4.968</v>
+        <v>-0.019455254</v>
       </c>
       <c r="BS2" t="n">
-        <v>-0.09160304</v>
+        <v>0.24487448</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.27294624</v>
+        <v>21.7</v>
       </c>
       <c r="BU2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="BV2" t="n">
         <v>1193788800</v>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>EQUITY</t>
         </is>
       </c>
-      <c r="BX2" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BY2" t="inlineStr">
+      <c r="BW2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BX2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
+      <c r="BY2" t="n">
+        <v>66043000</v>
+      </c>
       <c r="BZ2" t="n">
-        <v>51080000</v>
+        <v>4.806</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.717</v>
+        <v>27758668</v>
       </c>
       <c r="CB2" t="n">
-        <v>2375000</v>
+        <v>991000</v>
       </c>
       <c r="CC2" t="n">
-        <v>1522000</v>
+        <v>8.679</v>
       </c>
       <c r="CD2" t="n">
-        <v>8.746</v>
+        <v>8.737</v>
       </c>
       <c r="CE2" t="n">
-        <v>8.789</v>
+        <v>20585000</v>
       </c>
       <c r="CF2" t="n">
-        <v>6646000</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="CG2" t="n">
-        <v>1.475</v>
+        <v>1.498</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.484</v>
+        <v>0.15275</v>
       </c>
       <c r="CI2" t="n">
-        <v>6501000</v>
+        <v>0.02406</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-1440000</v>
+        <v>18928000</v>
       </c>
       <c r="CK2" t="n">
-        <v>-0.006</v>
+        <v>19982500</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.97818</v>
+        <v>4196000</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.35736</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.28855</v>
-      </c>
-      <c r="CO2" t="inlineStr">
+        <v>0.9195</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>1.34849</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>-0.41992</v>
+      </c>
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>PLN</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>06N.WA</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>en-US</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="CS2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="CT2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>Delayed Quote</t>
         </is>
       </c>
-      <c r="CU2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CV2" t="inlineStr">
+      <c r="CW2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CX2" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="CW2" t="inlineStr">
-        <is>
-          <t>POSTPOST</t>
-        </is>
-      </c>
-      <c r="CX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY2" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="CZ2" t="inlineStr">
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="CZ2" t="n">
+        <v>-0.79365003</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DB2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>1266825600000</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>-0.01999998</v>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>2.46 - 2.52</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>Warsaw</t>
+        </is>
+      </c>
+      <c r="DG2" t="n">
+        <v>6231</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>0.17000008</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>0.07296140499999999</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>2.33 - 3.44</t>
+        </is>
+      </c>
+      <c r="DK2" t="n">
+        <v>-0.94000006</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>-0.27325583</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>-1.9455254</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>0.07139993</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>0.029399624</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-0.096050024</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>-0.036998525</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>06MAGNA</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
         <is>
           <t>Magna Polonia S.A.</t>
         </is>
       </c>
-      <c r="DA2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DX2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DE2" t="n">
-        <v>1780407322</v>
-      </c>
-      <c r="DF2" t="inlineStr">
+      <c r="DY2" t="n">
+        <v>1782140401</v>
+      </c>
+      <c r="DZ2" t="inlineStr">
         <is>
           <t>WSE</t>
         </is>
       </c>
-      <c r="DG2" t="inlineStr">
+      <c r="EA2" t="inlineStr">
         <is>
           <t>finmb_3483482</t>
         </is>
       </c>
-      <c r="DH2" t="inlineStr">
+      <c r="EB2" t="inlineStr">
         <is>
           <t>Europe/Warsaw</t>
         </is>
       </c>
-      <c r="DI2" t="inlineStr">
+      <c r="EC2" t="inlineStr">
         <is>
           <t>CEST</t>
         </is>
       </c>
-      <c r="DJ2" t="n">
+      <c r="ED2" t="n">
         <v>7200000</v>
       </c>
-      <c r="DK2" t="inlineStr">
+      <c r="EE2" t="inlineStr">
         <is>
           <t>pl_market</t>
         </is>
       </c>
-      <c r="DL2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>06MAGNA</t>
-        </is>
-      </c>
-      <c r="DN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>1266825600000</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>2.35 - 2.38</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>Warsaw</t>
-        </is>
-      </c>
-      <c r="DS2" t="n">
-        <v>6855</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>0.05000019</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>0.02145931</v>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>2.33 - 3.44</t>
-        </is>
-      </c>
-      <c r="DW2" t="n">
-        <v>-1.06</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-0.3081395</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>-9.160304</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>-0.052599907</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>-0.021622917</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>-0.21669984</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>-0.083452016</v>
-      </c>
-      <c r="EE2" t="inlineStr"/>
+      <c r="EF2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EG2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
